--- a/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/cs-cz.xlsx
+++ b/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/cs-cz.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Documents\_Learn\Packaging.tutorial\OS.11\23H2\Expand\Install\Report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5924f5d6bcb7c7fc/Documents/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE63754-E404-4033-9F1F-628ECCD8F6B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{3EE63754-E404-4033-9F1F-628ECCD8F6B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49CFD786-CFAB-46B0-A722-A34D891F2B5F}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="27634" windowHeight="16629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6499,7 +6499,7 @@
     <col min="2" max="2" width="0.84375" style="3" customWidth="1"/>
     <col min="3" max="3" width="84.69140625" style="3" customWidth="1"/>
     <col min="4" max="4" width="50.3828125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.53515625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="20.53515625" style="15" customWidth="1"/>
     <col min="6" max="6" width="16.69140625" style="3" customWidth="1"/>
     <col min="7" max="7" width="120.69140625" style="3" customWidth="1"/>
     <col min="8" max="10" width="16.69140625" style="3" customWidth="1"/>
@@ -6539,6 +6539,7 @@
       <c r="A3" s="1"/>
       <c r="C3" s="7"/>
       <c r="D3" s="5"/>
+      <c r="E3" s="3"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="2"/>
@@ -6550,6 +6551,7 @@
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
+      <c r="E4" s="3"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="9"/>
@@ -6644,12 +6646,12 @@
     <row r="8" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C8" s="14"/>
       <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
     </row>
     <row r="9" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="17"/>
@@ -6659,6 +6661,12 @@
       <c r="D9" s="19" t="s">
         <v>5</v>
       </c>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
     </row>
     <row r="10" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B10" s="20"/>
@@ -6668,12 +6676,12 @@
       <c r="D10" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
     </row>
     <row r="11" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="22"/>
@@ -6683,27 +6691,26 @@
       <c r="D11" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
     </row>
     <row r="12" spans="1:12" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
     </row>
     <row r="13" spans="1:12" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
     </row>
@@ -6711,7 +6718,7 @@
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
+      <c r="E14" s="15"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
@@ -6722,7 +6729,7 @@
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
+      <c r="E15" s="15"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
@@ -6733,7 +6740,7 @@
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
+      <c r="E16" s="15"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
@@ -6744,7 +6751,7 @@
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
+      <c r="E17" s="15"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
@@ -6755,7 +6762,7 @@
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
+      <c r="E18" s="15"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
@@ -6766,7 +6773,7 @@
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
+      <c r="E19" s="15"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
@@ -6777,7 +6784,7 @@
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
+      <c r="E20" s="15"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
@@ -6788,7 +6795,7 @@
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
+      <c r="E21" s="15"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
@@ -6799,7 +6806,7 @@
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
+      <c r="E22" s="15"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
@@ -6810,7 +6817,7 @@
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
+      <c r="E23" s="15"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
@@ -6821,7 +6828,7 @@
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
+      <c r="E24" s="15"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -6832,7 +6839,7 @@
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
+      <c r="E25" s="15"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
@@ -6843,7 +6850,7 @@
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
+      <c r="E26" s="15"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
@@ -6854,7 +6861,7 @@
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
+      <c r="E27" s="15"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
@@ -6865,7 +6872,7 @@
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
+      <c r="E28" s="15"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
@@ -6876,7 +6883,7 @@
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
+      <c r="E29" s="15"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
@@ -6887,7 +6894,7 @@
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
+      <c r="E30" s="15"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
@@ -6898,7 +6905,7 @@
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
+      <c r="E31" s="15"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
@@ -6909,7 +6916,7 @@
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
+      <c r="E32" s="15"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
@@ -6920,7 +6927,7 @@
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
+      <c r="E33" s="15"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
@@ -6931,7 +6938,7 @@
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
+      <c r="E34" s="15"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
@@ -6941,7 +6948,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <dataConsolidate/>
-  <conditionalFormatting sqref="F8:I1048576 F1:I1 H2:I2 H3:J5">
+  <conditionalFormatting sqref="F13:I1048576 F1:I1 H2:I2 H3:J5">
     <cfRule type="iconSet" priority="282">
       <iconSet iconSet="3Symbols2" showValue="0">
         <cfvo type="percent" val="0"/>
@@ -6960,7 +6967,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:I8 H6:J7" xr:uid="{23AE6323-BC7F-40E9-A5AD-9DE77137CC3B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6:J7" xr:uid="{23AE6323-BC7F-40E9-A5AD-9DE77137CC3B}">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>
